--- a/NO_MPLS_SAD/demo_no_mpls.xlsx
+++ b/NO_MPLS_SAD/demo_no_mpls.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yonat\Videos\INI\NO_MPLS_SAD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC15BA2D-9563-4D32-88C5-C54080FF67F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6EC739-9A78-4A43-BDFF-45249EBE7A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25695" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Site 1 (HUB)" sheetId="1" r:id="rId1"/>
     <sheet name="Site 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Site 3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="58">
   <si>
     <t>site</t>
   </si>
@@ -211,18 +212,6 @@
     <t>tunnel 20</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20.1</t>
-  </si>
-  <si>
     <t>ISP-VLAN</t>
   </si>
   <si>
@@ -231,12 +220,24 @@
   <si>
     <t>tacacs_key</t>
   </si>
+  <si>
+    <t>num_downlink</t>
+  </si>
+  <si>
+    <t>20.0-30.0</t>
+  </si>
+  <si>
+    <t>DHCP</t>
+  </si>
+  <si>
+    <t>20.1-200.1</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -310,6 +311,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -331,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -377,14 +384,23 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="128">
+  <dxfs count="171">
     <dxf>
       <font>
         <b val="0"/>
@@ -405,6 +421,13 @@
     </dxf>
     <dxf>
       <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -419,73 +442,13 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <color theme="1"/>
       </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -507,6 +470,255 @@
     </dxf>
     <dxf>
       <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -521,7 +733,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -539,7 +751,63 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -561,6 +829,12 @@
     </dxf>
     <dxf>
       <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -597,6 +871,12 @@
     </dxf>
     <dxf>
       <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -615,6 +895,13 @@
     </dxf>
     <dxf>
       <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -633,37 +920,6 @@
     </dxf>
     <dxf>
       <font>
-        <color theme="1"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
         <sz val="11"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -671,9 +927,44 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
         <sz val="11"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -701,55 +992,17 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
         <sz val="11"/>
+        <color theme="1"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -780,72 +1033,30 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -863,7 +1074,25 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -882,6 +1111,333 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="11"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1544,100 +2100,100 @@
   </dxfs>
   <tableStyles count="16">
     <tableStyle name="Site 1 (HUB)-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="127"/>
-      <tableStyleElement type="headerRow" dxfId="126"/>
-      <tableStyleElement type="firstRowStripe" dxfId="125"/>
-      <tableStyleElement type="secondRowStripe" dxfId="124"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="170"/>
+      <tableStyleElement type="headerRow" dxfId="169"/>
+      <tableStyleElement type="firstRowStripe" dxfId="168"/>
+      <tableStyleElement type="secondRowStripe" dxfId="167"/>
     </tableStyle>
     <tableStyle name="Site 3-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="123"/>
-      <tableStyleElement type="headerRow" dxfId="122"/>
-      <tableStyleElement type="firstRowStripe" dxfId="121"/>
-      <tableStyleElement type="secondRowStripe" dxfId="120"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="166"/>
+      <tableStyleElement type="headerRow" dxfId="165"/>
+      <tableStyleElement type="firstRowStripe" dxfId="164"/>
+      <tableStyleElement type="secondRowStripe" dxfId="163"/>
     </tableStyle>
     <tableStyle name="Site 2-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="119"/>
-      <tableStyleElement type="headerRow" dxfId="118"/>
-      <tableStyleElement type="firstRowStripe" dxfId="117"/>
-      <tableStyleElement type="secondRowStripe" dxfId="116"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="162"/>
+      <tableStyleElement type="headerRow" dxfId="161"/>
+      <tableStyleElement type="firstRowStripe" dxfId="160"/>
+      <tableStyleElement type="secondRowStripe" dxfId="159"/>
     </tableStyle>
     <tableStyle name="Site 4-style" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="115"/>
-      <tableStyleElement type="headerRow" dxfId="114"/>
-      <tableStyleElement type="firstRowStripe" dxfId="113"/>
-      <tableStyleElement type="secondRowStripe" dxfId="112"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="158"/>
+      <tableStyleElement type="headerRow" dxfId="157"/>
+      <tableStyleElement type="firstRowStripe" dxfId="156"/>
+      <tableStyleElement type="secondRowStripe" dxfId="155"/>
     </tableStyle>
     <tableStyle name="Site 3-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="111"/>
-      <tableStyleElement type="headerRow" dxfId="110"/>
-      <tableStyleElement type="firstRowStripe" dxfId="109"/>
-      <tableStyleElement type="secondRowStripe" dxfId="108"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="154"/>
+      <tableStyleElement type="headerRow" dxfId="153"/>
+      <tableStyleElement type="firstRowStripe" dxfId="152"/>
+      <tableStyleElement type="secondRowStripe" dxfId="151"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="107"/>
-      <tableStyleElement type="headerRow" dxfId="106"/>
-      <tableStyleElement type="firstRowStripe" dxfId="105"/>
-      <tableStyleElement type="secondRowStripe" dxfId="104"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="150"/>
+      <tableStyleElement type="headerRow" dxfId="149"/>
+      <tableStyleElement type="firstRowStripe" dxfId="148"/>
+      <tableStyleElement type="secondRowStripe" dxfId="147"/>
     </tableStyle>
     <tableStyle name="Site 2-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="103"/>
-      <tableStyleElement type="headerRow" dxfId="102"/>
-      <tableStyleElement type="firstRowStripe" dxfId="101"/>
-      <tableStyleElement type="secondRowStripe" dxfId="100"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="146"/>
+      <tableStyleElement type="headerRow" dxfId="145"/>
+      <tableStyleElement type="firstRowStripe" dxfId="144"/>
+      <tableStyleElement type="secondRowStripe" dxfId="143"/>
     </tableStyle>
     <tableStyle name="Site 3-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="99"/>
-      <tableStyleElement type="headerRow" dxfId="98"/>
-      <tableStyleElement type="firstRowStripe" dxfId="97"/>
-      <tableStyleElement type="secondRowStripe" dxfId="96"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="142"/>
+      <tableStyleElement type="headerRow" dxfId="141"/>
+      <tableStyleElement type="firstRowStripe" dxfId="140"/>
+      <tableStyleElement type="secondRowStripe" dxfId="139"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="95"/>
-      <tableStyleElement type="headerRow" dxfId="94"/>
-      <tableStyleElement type="firstRowStripe" dxfId="93"/>
-      <tableStyleElement type="secondRowStripe" dxfId="92"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="138"/>
+      <tableStyleElement type="headerRow" dxfId="137"/>
+      <tableStyleElement type="firstRowStripe" dxfId="136"/>
+      <tableStyleElement type="secondRowStripe" dxfId="135"/>
     </tableStyle>
     <tableStyle name="Site 4-style 2" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF09000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="91"/>
-      <tableStyleElement type="headerRow" dxfId="90"/>
-      <tableStyleElement type="firstRowStripe" dxfId="89"/>
-      <tableStyleElement type="secondRowStripe" dxfId="88"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="134"/>
+      <tableStyleElement type="headerRow" dxfId="133"/>
+      <tableStyleElement type="firstRowStripe" dxfId="132"/>
+      <tableStyleElement type="secondRowStripe" dxfId="131"/>
     </tableStyle>
     <tableStyle name="Site 3-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0A000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="87"/>
-      <tableStyleElement type="headerRow" dxfId="86"/>
-      <tableStyleElement type="firstRowStripe" dxfId="85"/>
-      <tableStyleElement type="secondRowStripe" dxfId="84"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="130"/>
+      <tableStyleElement type="headerRow" dxfId="129"/>
+      <tableStyleElement type="firstRowStripe" dxfId="128"/>
+      <tableStyleElement type="secondRowStripe" dxfId="127"/>
     </tableStyle>
     <tableStyle name="Site 1 (HUB)-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0B000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="83"/>
-      <tableStyleElement type="headerRow" dxfId="82"/>
-      <tableStyleElement type="firstRowStripe" dxfId="81"/>
-      <tableStyleElement type="secondRowStripe" dxfId="80"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="126"/>
+      <tableStyleElement type="headerRow" dxfId="125"/>
+      <tableStyleElement type="firstRowStripe" dxfId="124"/>
+      <tableStyleElement type="secondRowStripe" dxfId="123"/>
     </tableStyle>
     <tableStyle name="Site 2-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0C000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="79"/>
-      <tableStyleElement type="headerRow" dxfId="78"/>
-      <tableStyleElement type="firstRowStripe" dxfId="77"/>
-      <tableStyleElement type="secondRowStripe" dxfId="76"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="122"/>
+      <tableStyleElement type="headerRow" dxfId="121"/>
+      <tableStyleElement type="firstRowStripe" dxfId="120"/>
+      <tableStyleElement type="secondRowStripe" dxfId="119"/>
     </tableStyle>
     <tableStyle name="Site 4-style 3" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0D000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="75"/>
-      <tableStyleElement type="headerRow" dxfId="74"/>
-      <tableStyleElement type="firstRowStripe" dxfId="73"/>
-      <tableStyleElement type="secondRowStripe" dxfId="72"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="118"/>
+      <tableStyleElement type="headerRow" dxfId="117"/>
+      <tableStyleElement type="firstRowStripe" dxfId="116"/>
+      <tableStyleElement type="secondRowStripe" dxfId="115"/>
     </tableStyle>
     <tableStyle name="Site 2-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0E000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="71"/>
-      <tableStyleElement type="headerRow" dxfId="70"/>
-      <tableStyleElement type="firstRowStripe" dxfId="69"/>
-      <tableStyleElement type="secondRowStripe" dxfId="68"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="114"/>
+      <tableStyleElement type="headerRow" dxfId="113"/>
+      <tableStyleElement type="firstRowStripe" dxfId="112"/>
+      <tableStyleElement type="secondRowStripe" dxfId="111"/>
     </tableStyle>
     <tableStyle name="Site 4-style 4" pivot="0" count="4" xr9:uid="{00000000-0011-0000-FFFF-FFFF0F000000}">
-      <tableStyleElement type="wholeTable" size="0" dxfId="67"/>
-      <tableStyleElement type="headerRow" dxfId="66"/>
-      <tableStyleElement type="firstRowStripe" dxfId="65"/>
-      <tableStyleElement type="secondRowStripe" dxfId="64"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="110"/>
+      <tableStyleElement type="headerRow" dxfId="109"/>
+      <tableStyleElement type="firstRowStripe" dxfId="108"/>
+      <tableStyleElement type="secondRowStripe" dxfId="107"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1652,16 +2208,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:H2">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabell5" displayName="Tabell5" ref="A1:I2">
+  <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="site"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="intf_prefix"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="router-id"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{754ADF79-920D-4601-911B-DB20F4E9EEB9}" name="secret" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{D293CCAB-D8AE-4182-83E6-F65F455FC5F2}" name="tacacs_key" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{754ADF79-920D-4601-911B-DB20F4E9EEB9}" name="secret" dataDxfId="82"/>
+    <tableColumn id="8" xr3:uid="{D293CCAB-D8AE-4182-83E6-F65F455FC5F2}" name="tacacs_key" dataDxfId="81"/>
+    <tableColumn id="9" xr3:uid="{A1409C6A-F30B-4031-ADB8-676C007D78B3}" name="DHCP" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Site 1 (HUB)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1676,7 +2233,7 @@
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+$A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="31">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="source" dataDxfId="103">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="destination"/>
@@ -1690,45 +2247,164 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A19:E20" headerRowDxfId="44" dataDxfId="43" totalsRowDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="29" xr:uid="{EA312CD4-9955-4DBC-87B3-6D788BE89D2E}" name="Tabell13192530" displayName="Tabell13192530" ref="A19:E20" headerRowDxfId="102" dataDxfId="101" totalsRowDxfId="100">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="41">
+    <tableColumn id="1" xr3:uid="{FCAD462F-C9DE-45E3-B342-8BC685D1666E}" name="site" dataDxfId="99">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="38" totalsRowDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{E8DA5B0D-4B09-4D1E-BDAB-BAC231407C4D}" name="secret" dataDxfId="36" totalsRowDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{A37D0432-8751-44ED-8106-422243C1F04B}" name="brukernavn" dataDxfId="98"/>
+    <tableColumn id="5" xr3:uid="{1A9A17E0-8442-4E89-96DC-BC0A8BECBBCA}" name="passord" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{F0C81F5E-B27A-43FB-83C1-1FEB580854DE}" name="vty_lines" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="2" xr3:uid="{E8DA5B0D-4B09-4D1E-BDAB-BAC231407C4D}" name="secret" dataDxfId="94" totalsRowDxfId="93"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A22:I24" totalsRowCount="1" headerRowDxfId="34" totalsRowDxfId="33">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" totalsRowLabel="2" dataDxfId="32" totalsRowDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1746730A-1530-4A6C-8C70-0F2C6BF9753C}" name="Tabell161824282" displayName="Tabell161824282" ref="A22:J24" totalsRowShown="0" headerRowDxfId="92" totalsRowDxfId="91">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{15F3A197-501D-4FB4-9993-D97C276F45D1}" name="SW" dataDxfId="90" totalsRowDxfId="67">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" totalsRowLabel="10" dataDxfId="28" totalsRowDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" totalsRowFunction="custom" dataDxfId="27" totalsRowDxfId="19">
+    <tableColumn id="2" xr3:uid="{74DD496A-588F-4B13-B651-6375E15475E0}" name="MGMT Vlan" dataDxfId="89" totalsRowDxfId="66"/>
+    <tableColumn id="3" xr3:uid="{DADAFDFC-5D9A-4BEF-83FF-73C8B73914A7}" name="MGMT ip" dataDxfId="88" totalsRowDxfId="65">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</calculatedColumnFormula>
-      <totalsRowFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" totalsRowFunction="custom" dataDxfId="26" totalsRowDxfId="18">
+    <tableColumn id="4" xr3:uid="{42D46B63-EECB-4A1E-9799-D2E7774B9BCD}" name="gateway" dataDxfId="87" totalsRowDxfId="64">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
-      <totalsRowFormula>$E$5</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" totalsRowFunction="custom" dataDxfId="25" totalsRowDxfId="17">
+    <tableColumn id="5" xr3:uid="{0BA7E9B1-43B9-44A7-AEF2-587DFD6DB8EE}" name="mask" dataDxfId="86" totalsRowDxfId="63">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
-      <totalsRowFormula>$F$5</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="vlan-antall" totalsRowLabel="20.1" dataDxfId="24" totalsRowDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="num_ports" totalsRowLabel="4" dataDxfId="23" totalsRowDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" totalsRowLabel="g0/" dataDxfId="22" totalsRowDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" totalsRowFunction="custom" dataDxfId="21" totalsRowDxfId="13">
-      <calculatedColumnFormula>$G23-3</calculatedColumnFormula>
-      <totalsRowFormula>$G24-3</totalsRowFormula>
+    <tableColumn id="10" xr3:uid="{ABE9A322-920A-45B2-8208-4C5BF949E975}" name="num_ports" dataDxfId="58" totalsRowDxfId="59"/>
+    <tableColumn id="6" xr3:uid="{5B7AA8BC-D315-4E8D-8528-C2AE65848FDF}" name="num_downlink" dataDxfId="85"/>
+    <tableColumn id="7" xr3:uid="{1088FF3C-FB1C-4E78-BE34-551D9AC36C3C}" name="vlan-antall" dataDxfId="57" totalsRowDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{19FD676B-E225-4461-8031-718593F85D50}" name="intf_prefix" dataDxfId="84" totalsRowDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{B26584E6-2A20-4139-9852-FBB25CD74431}" name="num_port_ledig" dataDxfId="83" totalsRowDxfId="61">
+      <calculatedColumnFormula>$F23-$G23-2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{9F39C48E-2E8B-4EBF-B634-E201347DA780}" name="Tabell17" displayName="Tabell17" ref="A1:H2">
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{18DB95AF-5409-4D55-A98E-A450CFCD75F0}" name="site"/>
+    <tableColumn id="2" xr3:uid="{58D21A86-CE00-4CF7-A835-0F8377E808C8}" name="intf_prefix"/>
+    <tableColumn id="3" xr3:uid="{382318A4-339C-4956-94BD-3C6C9F9E2FDB}" name="router-id">
+      <calculatedColumnFormula>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{D7A234D3-034E-4A19-A6E5-CCCB9F321ED9}" name="brukernavn"/>
+    <tableColumn id="5" xr3:uid="{DD769197-A270-487E-AABC-F725CDF48CE0}" name="passord"/>
+    <tableColumn id="6" xr3:uid="{0EA78CCF-491B-420A-B7E5-6F29E67F83B7}" name="vty_lines"/>
+    <tableColumn id="7" xr3:uid="{A43BA295-35BB-4986-AAA0-82BA2930E97C}" name="secret" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{4845DF5C-DFFF-455A-891F-443886F5F91B}" name="tacacs_key" dataDxfId="34">
+      <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{B11FC9E7-1FFA-4B8E-AEB2-732A7646BE00}" name="Tabell29" displayName="Tabell29" ref="A4:K7">
+  <tableColumns count="11">
+    <tableColumn id="1" xr3:uid="{064B279E-641A-4EE5-A064-CFFE5E067459}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{E0B710D3-9B8E-418B-8998-BC4F9E380718}" name="vlan"/>
+    <tableColumn id="3" xr3:uid="{0BEF9D25-445F-4B19-8AAE-43280CE9CB02}" name="interface"/>
+    <tableColumn id="4" xr3:uid="{851D5E8A-B992-4888-929D-FBE6B992DB13}" name="nett id"/>
+    <tableColumn id="5" xr3:uid="{DC674619-E469-4550-967E-FB6B32707663}" name="gateway">
+      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{4E37D5CC-2F42-470C-AF6B-734AA2E55B33}" name="mask"/>
+    <tableColumn id="7" xr3:uid="{D2468390-B84D-4BD9-AA0C-167CCDF9E92D}" name="address min">
+      <calculatedColumnFormula>LEFT(D5,LEN(D5)-1)&amp;"1"</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" xr3:uid="{91D6E7D8-B3AC-437A-A785-412053F8E223}" name="address max"/>
+    <tableColumn id="9" xr3:uid="{F41034B6-4D6A-483F-ABCB-4137DA01DE30}" name="antall-res" dataDxfId="33"/>
+    <tableColumn id="10" xr3:uid="{6EDA0C76-8808-4526-96CD-F74F717D6C42}" name="pri-afxx"/>
+    <tableColumn id="11" xr3:uid="{740A9BAE-AF16-4206-A97C-7FC36DF740DF}" name="pri-1-10"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{22BC4639-44FB-4EF2-9834-80FF30A80A9C}" name="Tabell310" displayName="Tabell310" ref="A9:D12">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{7ED75EBE-39D6-406F-92D5-9C841E41C3C2}" name="vrf"/>
+    <tableColumn id="2" xr3:uid="{0A545ED0-4AEA-404F-9D43-264B7E287830}" name="rt"/>
+    <tableColumn id="3" xr3:uid="{E4392328-D89B-40D3-8B4B-C79E71EDAE51}" name="loopback"/>
+    <tableColumn id="4" xr3:uid="{BB0B63EE-43E1-44D6-9F89-98A53DB62F05}" name="laddr"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{F2C1E509-29FA-467D-B098-6A22A014CC9F}" name="Tabell412" displayName="Tabell412" ref="A14:J17">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{E7273145-0FE2-4481-8411-F4837D6B9B49}" name="tunnel id"/>
+    <tableColumn id="2" xr3:uid="{9DC2EEA6-0F71-45A0-9B23-87B7732D5683}" name="vrf"/>
+    <tableColumn id="3" xr3:uid="{B248E884-35ED-4614-845A-87AE65E5A1ED}" name="ip address">
+      <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+$A$2)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{9FB1675A-D623-40C0-86FE-275F737ED9AD}" name="mask"/>
+    <tableColumn id="5" xr3:uid="{96D9656A-2264-4FEA-ACB7-01A5DC848DF3}" name="source" dataDxfId="32">
+      <calculatedColumnFormula>$C$2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="6" xr3:uid="{620A2335-1FAB-4021-9550-A897969055EC}" name="destination"/>
+    <tableColumn id="7" xr3:uid="{5358F0DF-6EF9-4238-AF75-F4A1596B138D}" name="gre mode"/>
+    <tableColumn id="8" xr3:uid="{D9CF5E59-48A0-4F4C-8A3E-8CF25AA87E33}" name="network-id"/>
+    <tableColumn id="9" xr3:uid="{F28CF941-942F-4757-98D7-A80635325D70}" name="ipsec">
+      <calculatedColumnFormula array="1">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{028E3FDD-2D4E-4900-94D5-DDF1452DE886}" name="ipsec key"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 2-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{6520ECA7-F9D6-48B0-A209-AF47810B0692}" name="Tabell1319253015" displayName="Tabell1319253015" ref="A19:E20" headerRowDxfId="31" dataDxfId="30" totalsRowDxfId="29">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{40794628-1B58-4441-A376-BFB9A5B89F67}" name="site" dataDxfId="28">
+      <calculatedColumnFormula>A2</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{1B11D2A4-9A10-42EA-850F-D6F6AC72498F}" name="brukernavn" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{34FD6A85-BE68-47B3-BB7D-E810F9F5DAD4}" name="passord" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{8EC423D8-8F10-497A-A01A-80146EC9F882}" name="vty_lines" dataDxfId="24" totalsRowDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{949799DB-164D-454E-932B-2A0A65C96512}" name="secret" dataDxfId="22" totalsRowDxfId="23"/>
+  </tableColumns>
+  <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{F1FEEE89-5472-4E46-842B-957BC7468053}" name="Tabell16182428217" displayName="Tabell16182428217" ref="A22:J24" totalsRowShown="0" headerRowDxfId="21" totalsRowDxfId="20">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{60C698D6-62E4-4F1B-94EA-0AAF8A6EEB3E}" name="SW" dataDxfId="18" totalsRowDxfId="19">
+      <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{A203A4AB-36C7-48F6-AB50-EDD2D57AAFFB}" name="MGMT Vlan" dataDxfId="16" totalsRowDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{F3FDF8CC-C4D4-4A09-8BD3-50AF06E48D2A}" name="MGMT ip" dataDxfId="14" totalsRowDxfId="15">
+      <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="4" xr3:uid="{C718C222-C221-4F1F-9450-440F7E212BC0}" name="gateway" dataDxfId="12" totalsRowDxfId="13">
+      <calculatedColumnFormula>$E$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="5" xr3:uid="{26EDA28B-CB04-4F5B-9722-A6710B4DF905}" name="mask" dataDxfId="10" totalsRowDxfId="11">
+      <calculatedColumnFormula>$F$5</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" xr3:uid="{A442DE84-E237-4A61-8C23-AD4BB16FF6DF}" name="num_ports" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{9C2FD180-858C-4945-B4D3-A0A1D6BEA732}" name="num_downlink" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{5B1E678B-E7D6-41A1-9323-D3234AEF8E5F}" name="vlan-antall" dataDxfId="5" totalsRowDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{87F33D81-D922-440C-A76B-6EF97A1CCE88}" name="intf_prefix" dataDxfId="3" totalsRowDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{FA1EFF52-322F-4DAF-8708-88501DE270EF}" name="num_port_ledig" dataDxfId="1" totalsRowDxfId="2">
+      <calculatedColumnFormula>$F23-$G23-2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Site 4-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -1746,7 +2422,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{CE1C3544-35AB-45BD-B168-A59522955D24}" name="antall-res" dataDxfId="80"/>
     <tableColumn id="10" xr3:uid="{5AE4CD65-C2FF-447E-B037-873FB4F36B65}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{BBB41126-CDAD-40BD-92C3-0A8EEC64127E}" name="pri-1-10"/>
   </tableColumns>
@@ -1775,7 +2451,7 @@
       <calculatedColumnFormula>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+$A$2)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="mask"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="30">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="source" dataDxfId="79">
       <calculatedColumnFormula>$C$2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="destination"/>
@@ -1789,42 +2465,43 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A19:F20" headerRowDxfId="61" dataDxfId="60" totalsRowDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{D9D18493-1508-418F-A690-377066CBE6D1}" name="Tabell131921" displayName="Tabell131921" ref="A19:F20" headerRowDxfId="78" dataDxfId="77" totalsRowDxfId="76">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="58">
+    <tableColumn id="1" xr3:uid="{2906F324-3A93-4FB9-9A3C-D48E0E017DE1}" name="site" dataDxfId="75">
       <calculatedColumnFormula>A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="57"/>
-    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="56"/>
-    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{E15E69AB-85DA-4C56-B495-1EB315268322}" name="secret" dataDxfId="54" totalsRowDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{AED40A1C-7FDA-4DCF-A52E-B4FC80E2A31D}" name="ISP-VLAN" dataDxfId="3" totalsRowDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{EACB8E41-CE14-43F2-9E46-F1D9E473C840}" name="brukernavn" dataDxfId="74"/>
+    <tableColumn id="4" xr3:uid="{BDD570DD-38B1-4E0D-8E69-41BC5527F423}" name="passord" dataDxfId="73"/>
+    <tableColumn id="5" xr3:uid="{0C9E5C25-E441-46FF-92BD-E2BEA9C8A2C6}" name="vty_lines" dataDxfId="72"/>
+    <tableColumn id="3" xr3:uid="{E15E69AB-85DA-4C56-B495-1EB315268322}" name="secret" dataDxfId="71" totalsRowDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{AED40A1C-7FDA-4DCF-A52E-B4FC80E2A31D}" name="ISP-VLAN" dataDxfId="69" totalsRowDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="Site 4-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="27" xr:uid="{80770F74-6AF8-4ED1-9361-404458E55511}" name="Tabell16182428" displayName="Tabell16182428" ref="A22:I23" headerRowDxfId="52" totalsRowDxfId="51">
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{1B73E0C7-C498-41F8-BAC8-7E845E00CB65}" name="SW" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{894D379E-7844-43E1-9A69-E543D4F66CAE}" name="Tabell1618242825" displayName="Tabell1618242825" ref="A22:J23" totalsRowShown="0" headerRowDxfId="56" totalsRowDxfId="55">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A639BB91-B12B-4EED-AE86-29FAEE230445}" name="SW" dataDxfId="53" totalsRowDxfId="54">
       <calculatedColumnFormula>(ROW())-(ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{55746631-7369-4BB6-92AF-BC912FBA9E5B}" name="MGMT Vlan" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{33D1D208-4592-452F-9EE7-3DD24275FDDC}" name="MGMT ip" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{DDEDC243-35DD-454B-A6C1-7C4D32FA2867}" name="MGMT Vlan" dataDxfId="51" totalsRowDxfId="52"/>
+    <tableColumn id="3" xr3:uid="{38DD73AF-4967-4DE7-9CD2-7469CCB16A5B}" name="MGMT ip" dataDxfId="49" totalsRowDxfId="50">
       <calculatedColumnFormula>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{300ED09A-B325-432A-824C-60A4545FEF10}" name="gateway" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{B639C5B3-A0C0-41EF-82FD-469668E690E4}" name="gateway" dataDxfId="47" totalsRowDxfId="48">
       <calculatedColumnFormula>$E$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{DE41E3AD-2DD4-4E00-AAA7-E16DA0B7B327}" name="mask" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{09CE4D96-47A5-4084-A00A-7E9FCF4320D1}" name="mask" dataDxfId="45" totalsRowDxfId="46">
       <calculatedColumnFormula>$F$5</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{10A4DA4A-2584-4B29-9285-F3E796366BC6}" name="vlan-antall" dataDxfId="7" totalsRowDxfId="50"/>
-    <tableColumn id="7" xr3:uid="{40A0DCDD-4793-4C04-AB5A-E199F256A0D9}" name="num_ports" dataDxfId="6" totalsRowDxfId="49"/>
-    <tableColumn id="8" xr3:uid="{D6B9E8CD-F7E4-4AF1-8D5B-45A78B5D62E7}" name="intf_prefix" dataDxfId="5" totalsRowDxfId="48"/>
-    <tableColumn id="9" xr3:uid="{03637906-AC3E-4DB7-AEDB-025CDAD6ADBA}" name="num_port_ledig" dataDxfId="4" totalsRowDxfId="47">
-      <calculatedColumnFormula>$G23-3</calculatedColumnFormula>
+    <tableColumn id="10" xr3:uid="{B3A08C44-D3F1-407C-80E1-7495A53A74A2}" name="num_ports" dataDxfId="43" totalsRowDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{2D1EE5FB-CC49-41F2-9AB4-1A3F983A3CA3}" name="num_downlink" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{5E9967C2-6052-41DD-8A9F-2F6A09502BCD}" name="vlan-antall" dataDxfId="40" totalsRowDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{77B04DFE-EDE0-479E-B0F4-8354D62C1E04}" name="intf_prefix" dataDxfId="38" totalsRowDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{46BF29F4-011C-4C0E-AE42-EC0A8E280964}" name="num_port_ledig" dataDxfId="36" totalsRowDxfId="37">
+      <calculatedColumnFormula>$F23-$G23-2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Site 4-style 4" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -1840,8 +2517,8 @@
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="brukernavn"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="passord"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="vty_lines"/>
-    <tableColumn id="7" xr3:uid="{AB00FC62-D408-4EC3-87DF-1FBB1D6A67CC}" name="secret" dataDxfId="46"/>
-    <tableColumn id="8" xr3:uid="{0CA8018F-103D-4C3A-B1A5-842F9330657B}" name="tacacs_key" dataDxfId="0">
+    <tableColumn id="7" xr3:uid="{AB00FC62-D408-4EC3-87DF-1FBB1D6A67CC}" name="secret" dataDxfId="106"/>
+    <tableColumn id="8" xr3:uid="{0CA8018F-103D-4C3A-B1A5-842F9330657B}" name="tacacs_key" dataDxfId="105">
       <calculatedColumnFormula>'Site 1 (HUB)'!H2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1860,7 +2537,7 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="mask"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="address min"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="address max"/>
-    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{FD71411A-F46A-4E62-B3D3-4B0E2ED5C489}" name="antall-res" dataDxfId="104"/>
     <tableColumn id="10" xr3:uid="{10BC51DC-9FCC-48A1-8D71-0913AE61C798}" name="pri-afxx"/>
     <tableColumn id="11" xr3:uid="{1CC9D42E-8B8D-4781-B4E6-7B024D0D4DB5}" name="pri-1-10"/>
   </tableColumns>
@@ -2090,6 +2767,7 @@
     <col min="5" max="6" width="12.5703125" customWidth="1"/>
     <col min="7" max="7" width="23.28515625" customWidth="1"/>
     <col min="9" max="9" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="37.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2115,7 +2793,10 @@
         <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2142,7 +2823,10 @@
         <v>49</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
+      </c>
+      <c r="I2" s="2" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -2515,7 +3199,7 @@
         <v>48</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2557,15 +3241,18 @@
         <v>13</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="10" t="s">
+      <c r="I22" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="J22" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2590,17 +3277,20 @@
         <v>255.255.0.0</v>
       </c>
       <c r="F23" s="6">
-        <v>200.1</v>
-      </c>
-      <c r="G23" s="11">
         <v>4</v>
       </c>
-      <c r="H23" s="11" t="s">
+      <c r="G23" s="16">
+        <v>0</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I23" s="11">
-        <f>$G23-3</f>
-        <v>1</v>
+      <c r="J23" s="11">
+        <f>$F23-$G23-2</f>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3583,8 +4273,8 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F23" xr:uid="{C587E448-31D9-47EB-8420-25A87965F050}">
-      <formula1>IF(F23="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F23,"-"),"."))&lt;=$G23-3)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23" xr:uid="{03BCF77C-42DF-4C47-A434-8A29680E17A5}">
+      <formula1>IF(H23="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(H23,"-"),"."))&lt;=J23)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -3640,7 +4330,7 @@
         <v>48</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4076,15 +4766,18 @@
         <v>13</v>
       </c>
       <c r="F22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G22" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="H22" s="10" t="s">
+      <c r="I22" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="J22" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4109,50 +4802,56 @@
         <v>255.255.0.0</v>
       </c>
       <c r="F23" s="6">
+        <v>4</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="G23" s="11">
-        <v>4</v>
-      </c>
-      <c r="H23" s="11" t="s">
+      <c r="I23" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I23" s="11">
-        <f>$G23-3</f>
+      <c r="J23" s="11">
+        <f>$F23-$G23-2</f>
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="6" t="str">
+      <c r="A24" s="16">
+        <v>2</v>
+      </c>
+      <c r="B24" s="16">
+        <v>10</v>
+      </c>
+      <c r="C24" s="18" t="str">
         <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
         <v>10.12.0.3</v>
       </c>
-      <c r="D24" s="6" t="str">
+      <c r="D24" s="18" t="str">
         <f>$E$5</f>
         <v>10.12.0.1</v>
       </c>
-      <c r="E24" s="6" t="str">
+      <c r="E24" s="16" t="str">
         <f>$F$5</f>
         <v>255.255.0.0</v>
       </c>
-      <c r="F24" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="H24" s="11" t="s">
+      <c r="F24" s="6">
+        <v>4</v>
+      </c>
+      <c r="G24" s="16">
+        <v>2</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="I24" s="11">
-        <f>$G24-3</f>
-        <v>1</v>
+      <c r="J24" s="20">
+        <f>$F24-$G24-2</f>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5128,8 +5827,8 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F23:F24" xr:uid="{755C67B3-35A1-41CF-AFAD-859DFFCA6014}">
-      <formula1>IF(F23="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(F23,"-"),"."))&lt;=$G23-3)</formula1>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23:H24" xr:uid="{755C67B3-35A1-41CF-AFAD-859DFFCA6014}">
+      <formula1>IF(H23="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(H23,"-"),"."))&lt;=J23)</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -5143,4 +5842,579 @@
     <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD6EE59D-AC84-4379-84CD-451968B2DD54}">
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" customWidth="1"/>
+    <col min="5" max="5" width="61" customWidth="1"/>
+    <col min="8" max="8" width="61.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;".0"</f>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="2" t="str">
+        <f>'Site 1 (HUB)'!H2</f>
+        <v>TACACS-KEY</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="3"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="7">
+        <v>10</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0</v>
+      </c>
+      <c r="D5" s="6" t="str">
+        <f>10&amp;"."&amp;(B5+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.13.0.0</v>
+      </c>
+      <c r="E5" s="6" t="str">
+        <f t="shared" ref="E5:E7" si="0">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="6" t="str">
+        <f t="shared" ref="G5:G7" si="1">LEFT(D5,LEN(D5)-1)&amp;"1"</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="H5" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D5,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.12.255.254")</f>
+        <v>10.12.255.254</v>
+      </c>
+      <c r="I5" s="6">
+        <v>10</v>
+      </c>
+      <c r="J5" s="15">
+        <v>21</v>
+      </c>
+      <c r="K5" s="15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7">
+        <v>20</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="str">
+        <f>10&amp;"."&amp;(B6+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.23.0.0</v>
+      </c>
+      <c r="E6" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>10.23.0.1</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>10.23.0.1</v>
+      </c>
+      <c r="H6" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D6,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.22.255.254")</f>
+        <v>10.22.255.254</v>
+      </c>
+      <c r="I6" s="6">
+        <v>10</v>
+      </c>
+      <c r="J6" s="15">
+        <v>11</v>
+      </c>
+      <c r="K6" s="15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0</v>
+      </c>
+      <c r="D7" s="6" t="str">
+        <f>10&amp;"."&amp;(B7+A2)&amp;"."&amp;0&amp;"."&amp;0</f>
+        <v>10.33.0.0</v>
+      </c>
+      <c r="E7" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v>10.33.0.1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="6" t="str">
+        <f t="shared" si="1"/>
+        <v>10.33.0.1</v>
+      </c>
+      <c r="H7" s="6" t="str">
+        <f ca="1">IFERROR(__xludf.DUMMYFUNCTION("REGEXREPLACE(D7,""\.[0-9]+\.[0-9]+$"","".255.254"")"),"10.32.255.254")</f>
+        <v>10.32.255.254</v>
+      </c>
+      <c r="I7" s="6">
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <v>41</v>
+      </c>
+      <c r="K7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="6">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C10)</f>
+        <v>3.3.3.10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="6">
+        <v>20</v>
+      </c>
+      <c r="D11" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C11)</f>
+        <v>3.3.3.20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6">
+        <v>30</v>
+      </c>
+      <c r="D12" s="6" t="str">
+        <f>A2&amp;"."&amp;A2&amp;"."&amp;A2&amp;"."&amp;(C12)</f>
+        <v>3.3.3.30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" s="13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A15" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="6" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H15+$A$2)</f>
+        <v>172.16.0.13</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E15" s="6" t="str">
+        <f t="shared" ref="E15:E17" si="2">$C$2</f>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H15" s="2">
+        <v>10</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="array" ref="I15">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A15 )*( 'Site 1 (HUB)'!B:B=B15 ),'Site 1 (HUB)'!I:I)</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:11" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H16+$A$2)</f>
+        <v>172.16.0.23</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H16" s="2">
+        <v>20</v>
+      </c>
+      <c r="I16" s="2" cm="1">
+        <f t="array" ref="I16">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A16 )*( 'Site 1 (HUB)'!B:B=B16 ),'Site 1 (HUB)'!I:I)</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="17" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="6" t="str">
+        <f>172&amp;"."&amp;16&amp;"."&amp;0&amp;"."&amp;(H17+$A$2)</f>
+        <v>172.16.0.33</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="6" t="str">
+        <f t="shared" si="2"/>
+        <v>3.3.3.0</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="2">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="b">
+        <f t="array" ref="I17">_xlfn.XLOOKUP(1,( 'Site 1 (HUB)'!A:A=A17 )*( 'Site 1 (HUB)'!B:B=B17 ),'Site 1 (HUB)'!I:I)</f>
+        <v>1</v>
+      </c>
+      <c r="J17" s="2"/>
+    </row>
+    <row r="19" spans="1:10" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="114.75" x14ac:dyDescent="0.2">
+      <c r="A20" s="11">
+        <f>A2</f>
+        <v>3</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="30" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="6">
+        <f>(ROW())-(ROW()-1)</f>
+        <v>1</v>
+      </c>
+      <c r="B23" s="6">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A23)</f>
+        <v>10.13.0.2</v>
+      </c>
+      <c r="D23" s="6" t="str">
+        <f>$E$5</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="E23" s="6" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F23" s="6">
+        <v>4</v>
+      </c>
+      <c r="G23" s="16">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J23" s="11">
+        <f>$F23-$G23-2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A24" s="16">
+        <v>2</v>
+      </c>
+      <c r="B24" s="16">
+        <v>10</v>
+      </c>
+      <c r="C24" s="18" t="str">
+        <f>LEFT($G$5,LEN($G$5)-1)&amp;(RIGHT($G$5,1)+A24)</f>
+        <v>10.13.0.3</v>
+      </c>
+      <c r="D24" s="18" t="str">
+        <f>$E$5</f>
+        <v>10.13.0.1</v>
+      </c>
+      <c r="E24" s="16" t="str">
+        <f>$F$5</f>
+        <v>255.255.0.0</v>
+      </c>
+      <c r="F24" s="6">
+        <v>4</v>
+      </c>
+      <c r="G24" s="16">
+        <v>2</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J24" s="20">
+        <f>$F24-$G24-2</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H23:H24" xr:uid="{2E979BD6-3A84-4B2E-9CEE-8F2B982BF6E0}">
+      <formula1>IF(H23="",TRUE,SUM(--_xlfn.TEXTAFTER(_xlfn.TEXTSPLIT(H23,"-"),"."))&lt;=J23)</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="6">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+  </tableParts>
+</worksheet>
 </file>